--- a/Data/Home/Bathroom.Light001.xlsx
+++ b/Data/Home/Bathroom.Light001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:I173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709283977</v>
+        <v>1711877410</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709284483</v>
+        <v>1711877938</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709243754</v>
+        <v>1711962387</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709244177</v>
+        <v>1711962979</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709245267</v>
+        <v>1711971574</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709245761</v>
+        <v>1711971801</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709329393</v>
+        <v>1711979179</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709329893</v>
+        <v>1711979877</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709417712</v>
+        <v>1712014082</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709418162</v>
+        <v>1712014707</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709446421</v>
+        <v>1712059822</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709448043</v>
+        <v>1712060376</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709454106</v>
+        <v>1712139808</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709454705</v>
+        <v>1712141404</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709501692</v>
+        <v>1712141671</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709502106</v>
+        <v>1712142209</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709588095</v>
+        <v>1712189098</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709588627</v>
+        <v>1712189711</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709621521</v>
+        <v>1712218060</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709622489</v>
+        <v>1712218653</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709628137</v>
+        <v>1712224216</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709628546</v>
+        <v>1712225342</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709680006</v>
+        <v>1712277025</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709680972</v>
+        <v>1712277723</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709682121</v>
+        <v>1712363728</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709682561</v>
+        <v>1712365749</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709692235</v>
+        <v>1712381504</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709692731</v>
+        <v>1712382851</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709693274</v>
+        <v>1712392817</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709694204</v>
+        <v>1712394325</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709701910</v>
+        <v>1712399872</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709702038</v>
+        <v>1712400413</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709710478</v>
+        <v>1712402096</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709711730</v>
+        <v>1712402654</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709786436</v>
+        <v>1712407984</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709786891</v>
+        <v>1712408614</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709792647</v>
+        <v>1712450048</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709793018</v>
+        <v>1712451679</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709796705</v>
+        <v>1712454551</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709797164</v>
+        <v>1712454669</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709851604</v>
+        <v>1712497446</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709851958</v>
+        <v>1712498900</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709879258</v>
+        <v>1712569259</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709879688</v>
+        <v>1712569828</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709935185</v>
+        <v>1712571441</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709935737</v>
+        <v>1712571999</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709937432</v>
+        <v>1712654803</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709937904</v>
+        <v>1712656687</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709964682</v>
+        <v>1712656986</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709965185</v>
+        <v>1712657569</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710033860</v>
+        <v>1712658850</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2360,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710034838</v>
+        <v>1712660549</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710050770</v>
+        <v>1712745144</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710052007</v>
+        <v>1712746227</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710053556</v>
+        <v>1712754285</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710054004</v>
+        <v>1712755761</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710150476</v>
+        <v>1712763251</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710150901</v>
+        <v>1712763850</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710195055</v>
+        <v>1712790431</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710195625</v>
+        <v>1712791094</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710197671</v>
+        <v>1712828591</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710198183</v>
+        <v>1712830525</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710225599</v>
+        <v>1712877115</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710226069</v>
+        <v>1712877661</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710234537</v>
+        <v>1712923376</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710236266</v>
+        <v>1712924008</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710242805</v>
+        <v>1712971572</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710243398</v>
+        <v>1712972199</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710300658</v>
+        <v>1712974483</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3026,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710301655</v>
+        <v>1712974576</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710317636</v>
+        <v>1712990354</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710318158</v>
+        <v>1712991026</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710324285</v>
+        <v>1712996552</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710324755</v>
+        <v>1712997096</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710374199</v>
+        <v>1712998995</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710374659</v>
+        <v>1712999670</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710400541</v>
+        <v>1713005574</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710401611</v>
+        <v>1713005849</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3359,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710406224</v>
+        <v>1713011183</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3396,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710406661</v>
+        <v>1713012859</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710454932</v>
+        <v>1713014086</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3470,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710455390</v>
+        <v>1713014660</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3507,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710486832</v>
+        <v>1713019251</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3544,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710487309</v>
+        <v>1713019870</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3581,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710541315</v>
+        <v>1713056843</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710541712</v>
+        <v>1713058357</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3655,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710570631</v>
+        <v>1713088818</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3692,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710572089</v>
+        <v>1713089279</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710576316</v>
+        <v>1713092993</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3766,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710576795</v>
+        <v>1713093571</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3803,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710578239</v>
+        <v>1713102459</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3840,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710578828</v>
+        <v>1713103117</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710712575</v>
+        <v>1713107974</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +3914,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710713063</v>
+        <v>1713108419</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +3951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710748175</v>
+        <v>1713137067</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +3988,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710749787</v>
+        <v>1713137629</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4025,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710755666</v>
+        <v>1713168257</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710756240</v>
+        <v>1713168828</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710830338</v>
+        <v>1713185519</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710830878</v>
+        <v>1713186035</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4173,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710835121</v>
+        <v>1713263826</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710835662</v>
+        <v>1713264406</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4247,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710900065</v>
+        <v>1713274999</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4284,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710901857</v>
+        <v>1713276218</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4321,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710919373</v>
+        <v>1713277052</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4358,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710920463</v>
+        <v>1713279038</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4395,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710922304</v>
+        <v>1713313424</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710922854</v>
+        <v>1713314036</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710924366</v>
+        <v>1713346541</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710924829</v>
+        <v>1713347862</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710928412</v>
+        <v>1713446692</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4580,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710928847</v>
+        <v>1713447272</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710975410</v>
+        <v>1713486710</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4654,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710977171</v>
+        <v>1713487212</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711000090</v>
+        <v>1713521117</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4728,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711000546</v>
+        <v>1713521477</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711004453</v>
+        <v>1713529333</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4802,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711004786</v>
+        <v>1713529866</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4839,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4858,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711006452</v>
+        <v>1713573607</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +4876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4895,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711006989</v>
+        <v>1713575372</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4913,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4932,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711007333</v>
+        <v>1713591674</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +4950,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4969,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711008996</v>
+        <v>1713593457</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +4987,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5006,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711085666</v>
+        <v>1713604072</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5024,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5043,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711087097</v>
+        <v>1713604633</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4933,6 +5061,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5080,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711146726</v>
+        <v>1713607996</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5098,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5117,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711147269</v>
+        <v>1713609224</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,6 +5135,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5023,7 +5154,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711182255</v>
+        <v>1713612159</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5041,6 +5172,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5059,7 +5191,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711184028</v>
+        <v>1713614043</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5077,6 +5209,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5228,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711232600</v>
+        <v>1713614960</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5113,6 +5246,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5131,7 +5265,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711233124</v>
+        <v>1713615524</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5149,6 +5283,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5167,7 +5302,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711274007</v>
+        <v>1713662179</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5185,6 +5320,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5203,7 +5339,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711274455</v>
+        <v>1713663628</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5221,6 +5357,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5376,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711322243</v>
+        <v>1713675592</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5257,6 +5394,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5413,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711322667</v>
+        <v>1713676583</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5293,6 +5431,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5450,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711353489</v>
+        <v>1713686819</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5329,6 +5468,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5347,7 +5487,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711355185</v>
+        <v>1713688376</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5365,6 +5505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5383,7 +5524,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711356529</v>
+        <v>1713689653</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5401,6 +5542,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5561,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711358134</v>
+        <v>1713690193</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5437,6 +5579,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5598,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711411871</v>
+        <v>1713700887</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5473,6 +5616,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5491,7 +5635,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711412597</v>
+        <v>1713702350</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5509,6 +5653,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5527,7 +5672,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711450963</v>
+        <v>1713874934</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5545,6 +5690,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5563,7 +5709,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711452408</v>
+        <v>1713875018</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5581,6 +5727,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5746,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711503314</v>
+        <v>1713962252</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5617,6 +5764,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5635,7 +5783,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711504733</v>
+        <v>1713962813</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5801,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +5820,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711530347</v>
+        <v>1714037527</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5689,6 +5838,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5707,7 +5857,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711531015</v>
+        <v>1714038757</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5725,6 +5875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5743,7 +5894,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711545561</v>
+        <v>1714052720</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5761,6 +5912,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +5931,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711546149</v>
+        <v>1714053275</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5797,6 +5949,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5815,7 +5968,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711605907</v>
+        <v>1714129259</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5833,6 +5986,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5851,7 +6005,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711607879</v>
+        <v>1714129830</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5869,6 +6023,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6042,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711608121</v>
+        <v>1714177777</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5905,6 +6060,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5923,7 +6079,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711608839</v>
+        <v>1714179182</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5941,6 +6097,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5959,7 +6116,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711620772</v>
+        <v>1714209617</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5977,6 +6134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6153,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711621470</v>
+        <v>1714210258</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6190,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711621837</v>
+        <v>1714212721</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6208,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6227,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711623576</v>
+        <v>1714214756</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6264,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711630019</v>
+        <v>1714217333</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6121,6 +6282,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6139,7 +6301,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711630590</v>
+        <v>1714217903</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6157,6 +6319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6338,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711634332</v>
+        <v>1714224085</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6356,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6375,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711634999</v>
+        <v>1714225464</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6229,6 +6393,451 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1714268949</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: on</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1714269564</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: off</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1714271861</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: on</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1714273735</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: off</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1714290154</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: on</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1714290736</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: off</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1714297115</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: on</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1714298474</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: off</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1714306534</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: on</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1714307751</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: off</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1714313056</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: on</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Light_Operation</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1714313607</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Bathroom.Light001.state: off</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
